--- a/Student_Performance_Data.xlsx
+++ b/Student_Performance_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\New folder (2)\Excel-Basics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA414BF-79CE-42C8-B84D-B7509BF7A0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD1E380-AACB-4BC9-81C6-BAF2034E38A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$1001</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -8583,16 +8586,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -8608,7 +8603,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -8616,78 +8611,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -8698,28 +8633,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8890EE44-9852-40AD-AE1E-230FD50D9BE6}" name="Table1" displayName="Table1" ref="A1:M1001" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
-  <autoFilter ref="A1:M1001" xr:uid="{8890EE44-9852-40AD-AE1E-230FD50D9BE6}"/>
-  <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{849F2013-7774-48DF-9BAF-04ADC7FACBBB}" name="Student ID"/>
-    <tableColumn id="2" xr3:uid="{4A8D98B9-22B4-4FF7-B89E-85CEEAB7E168}" name="Name"/>
-    <tableColumn id="16" xr3:uid="{7923DF89-065E-4972-A7A5-D4637421129D}" name="Fname"/>
-    <tableColumn id="15" xr3:uid="{6C558EDC-4DD0-40D9-AEF2-917EE57A5D27}" name="Lname"/>
-    <tableColumn id="3" xr3:uid="{AB8E47D7-F88B-4248-852F-6800DB0C40D6}" name="Gender"/>
-    <tableColumn id="4" xr3:uid="{15C510B0-5497-4617-B52A-3DC92ED27E67}" name="Age"/>
-    <tableColumn id="5" xr3:uid="{1C3CA49A-D4D5-44C6-9C33-9786FD88BEC6}" name="School"/>
-    <tableColumn id="6" xr3:uid="{BE98FB8F-2C19-4E0B-A2B3-D77577DDA022}" name="Class"/>
-    <tableColumn id="7" xr3:uid="{DD9BE3E2-DDA4-481F-B853-BD8318ABC1AD}" name="Subject"/>
-    <tableColumn id="8" xr3:uid="{58895A04-0EF5-4992-B5D5-F439CF594F7A}" name="Exam Type"/>
-    <tableColumn id="9" xr3:uid="{E7802D56-E1C7-4D21-A12E-9DDD2FBBE48A}" name="Score"/>
-    <tableColumn id="10" xr3:uid="{900B9643-A73A-4117-89B3-42E3379A93D3}" name="Teacher"/>
-    <tableColumn id="11" xr3:uid="{8C3494B0-38E2-4E3E-A18A-24FCDF3DCA05}" name="Pass"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9024,43 +8937,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>2846</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>2847</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -9655,10 +9568,6 @@
       <c r="M15" t="s">
         <v>2035</v>
       </c>
-      <c r="Q15">
-        <f>SUM(K16)</f>
-        <v>40</v>
-      </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -50089,10 +49998,8 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M1001" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 

--- a/Student_Performance_Data.xlsx
+++ b/Student_Performance_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\New folder (2)\Excel-Basics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD1E380-AACB-4BC9-81C6-BAF2034E38A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A247D75E-07A8-4779-82CE-68AB3B14ED7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
